--- a/Excel/map.xlsx
+++ b/Excel/map.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t/>
   </si>
@@ -58,6 +58,24 @@
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>黑松林</t>
+  </si>
+  <si>
+    <t>石牙矿洞</t>
+  </si>
+  <si>
+    <t>沉雾沼泽</t>
+  </si>
+  <si>
+    <t>白骨古墓</t>
+  </si>
+  <si>
+    <t>黑曜城堡</t>
+  </si>
+  <si>
+    <t>酒馆</t>
   </si>
 </sst>
 </file>
@@ -108,7 +126,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -123,6 +141,9 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles>
@@ -370,7 +391,7 @@
   <sheetPr>
     <tabColor/>
   </sheetPr>
-  <dimension ref="E4"/>
+  <dimension ref="E10"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.1836" customWidth="1"/>
@@ -441,6 +462,90 @@
         <v>5</v>
       </c>
     </row>
+    <row r="5" spans="2:5">
+      <c r="B5" s="5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="5">
+        <v>3</v>
+      </c>
+      <c r="E5" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="B6" s="5">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="5">
+        <v>7</v>
+      </c>
+      <c r="E6" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="B7" s="5">
+        <v>4</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2</v>
+      </c>
+      <c r="E7" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="B8" s="5">
+        <v>5</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="5">
+        <v>7</v>
+      </c>
+      <c r="E8" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9" s="5">
+        <v>6</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="5">
+        <v>9</v>
+      </c>
+      <c r="E9" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="B10" s="5">
+        <v>7</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="5">
+        <v>5</v>
+      </c>
+      <c r="E10" s="5">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>